--- a/reports/Bin_Stations_in_Food_Courts_Details_2026.xlsx
+++ b/reports/Bin_Stations_in_Food_Courts_Details_2026.xlsx
@@ -12,7 +12,16 @@
     <sheet name="SF FC Bin Spares" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="LG FC Bin Spares" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'SF FC Bin Stations'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'SF FC Bin Stations'!$A$1:$I$20</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'LG FC Bin Stations'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'LG FC Bin Stations'!$A$1:$I$8</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'SF FC Bin Spares'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'SF FC Bin Spares'!$A$1:$F$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'LG FC Bin Spares'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'LG FC Bin Spares'!$A$1:$F$4</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -1253,7 +1262,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1788,6 +1797,7 @@
     <mergeCell ref="A1:A2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
@@ -1796,7 +1806,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -2026,6 +2036,7 @@
     <mergeCell ref="A1:A2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
@@ -2034,7 +2045,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -2133,6 +2144,7 @@
     <mergeCell ref="A1:A2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
@@ -2141,7 +2153,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -2242,6 +2254,7 @@
     <mergeCell ref="A1:A2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>